--- a/dummy.xlsx
+++ b/dummy.xlsx
@@ -1290,7 +1290,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
-        <v>45777.6180555556</v>
+        <v>45772.6180555556</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
